--- a/CE国試data/CE_questions_2024.xlsx
+++ b/CE国試data/CE_questions_2024.xlsx
@@ -1378,7 +1378,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T151" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T172" t="inlineStr">
